--- a/data/trans_bre/IP07B_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP07B_R-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>4,32</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-1,18</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7,18</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>23,09</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,86%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-1,57%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,23%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>49,94%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>4.320312763536716</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.18434229082659</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>7.184378511950273</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>23.09410177400052</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.06864346239440845</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.01571961127723681</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.09225549446809722</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.4994126691082834</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-10,05; 18,06</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-14,95; 12,32</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-5,7; 19,08</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,29; 47,43</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-14,56; 32,53</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-18,94; 18,14</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-6,49; 27,39</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1,05; 164,99</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-10.05304575691375</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-14.94993008116968</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-5.704514625321599</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0.2918800430476527</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.1455770407670948</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.1893984048768755</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.0648572342218021</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>0.01048807359418159</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>18.05873487054604</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>12.32296324817318</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>19.07572844589968</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>47.43258265803219</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.3253112690488139</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.1814234366007295</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.2739290438562392</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>1.649910632005429</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>10,39</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-7,11</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-3,37</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>11,93</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>13,8%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-9,04%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-3,87%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>21,68%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>0,55; 19,45</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-17,21; 3,85</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-11,72; 5,04</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-2,64; 25,66</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,76; 28,12</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-20,62; 5,46</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-13,01; 6,1</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-4,11; 53,98</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>10.38990514683367</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-7.105098988849878</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-3.36706416855771</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>11.92619036956076</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.1380349373624451</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.09038339425403374</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.03867915883128443</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.2168423653186596</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,81</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>8,99</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6,47</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,07</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>13,08%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,74%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.5532098982610857</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-17.20895806821477</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-11.71802107234519</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-2.642407193660916</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0.007555763799659399</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.2062094728719863</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.1301407735254786</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.0411183874130759</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-11,12; 11,72</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-3,3; 20,71</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-2,5; 16,16</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-13,43; 21,95</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-12,83; 16,48</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-4,32; 33,53</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-2,83; 21,21</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-18,08; 38,72</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>19.45126286227505</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3.85051038232047</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>5.037901461863821</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>25.65705770909459</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.2811789768311051</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.0545712712007293</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.06104395692634611</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.5397742361297641</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-8,99</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-1,53</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,59</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-10,43</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-10,88%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-2,31%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-13,88%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.8078385739294314</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>8.989806171222813</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>6.470035338484137</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>3.065661781406703</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.01040901440347518</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.1308264474463502</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.07735941459797525</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.04590195931159281</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-19,76; 1,25</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-14,03; 10,28</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-9,67; 10,95</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-24,52; 5,64</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-22,92; 1,58</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-19,89; 17,52</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-11,3; 14,88</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-30,62; 8,49</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-11.12166063786477</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-3.296332617883231</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-2.502234440589334</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-13.42810808150803</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.128296609784504</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.04315753368137417</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.02830408991165869</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.1807527833060383</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>11.72039235766563</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>20.70945325154737</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>16.15590645570136</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>21.95275002171613</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.1648039397567379</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.3353141863576132</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.212078991238438</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.3871938815272212</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-8.985640519990101</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.527692762386001</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.5902671705221407</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-10.4325857298882</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.1087527837921647</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.02310507675250663</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.007431003350147832</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.1387829002046287</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-19.75978759620564</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-14.02524410597609</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-9.671153038932955</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-24.51815284501455</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.2292074020235337</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.1988831690228799</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.1130124986951473</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.3061613249894314</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.250143494821215</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>10.28359844122182</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>10.94711575850471</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>5.63663052587155</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.01578745533106578</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.1751752990049964</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.1488328905179074</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.084857481605969</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>2,33</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,91</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,85</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>6,98</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,11%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-1,27%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>11,54%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-3,29; 7,84</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-6,89; 5,14</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-3,63; 6,44</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-1,39; 16,11</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-4,13; 10,75</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-9,15; 7,39</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-4,41; 8,13</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-2,17; 29,83</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>2.33469743258008</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.9148064283611035</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.846761306379352</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>6.977610046085503</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.03109063332127218</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.01265204131418883</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.02244353353207117</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.1153746121960451</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-3.288548727368842</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-6.890190382440007</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-3.63181690645994</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.391655288408511</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.04126254752211242</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.09151345240261692</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.04407075446241911</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.02166209500842432</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>7.838969169407325</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>5.144292900070104</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>6.442120832788077</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>16.10560359550835</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.1075143071863551</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.07391672575594196</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.08127743754118168</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.2982686769489881</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
